--- a/outputs/01a05b96-e9d2-7420-b70e-419ec80490bc/대한민국_소주_제조사_생산자등록_조사_2026.xlsx
+++ b/outputs/01a05b96-e9d2-7420-b70e-419ec80490bc/대한민국_소주_제조사_생산자등록_조사_2026.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" r:id="Rbf00211c6ec2423d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="등록용_확정" sheetId="2" r:id="Re2c7f0a629274c51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검토필요_후보" sheetId="3" r:id="Raa1efde585ca4fd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제외_중복" sheetId="4" r:id="Rdf31302c7b6142eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조사기준" sheetId="5" r:id="Rd0b6e92b16684fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" r:id="R4f518a748ae34044"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="등록용_확정" sheetId="2" r:id="Ra3756704dd814974"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검토필요_후보" sheetId="3" r:id="R708c888a781b4576"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제외_중복" sheetId="4" r:id="Rd4bcafe2588440f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조사기준" sheetId="5" r:id="R6a8011b89093445d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -996,10 +996,10 @@
       </x:c>
       <x:c r="H5" s="17" t="str"/>
       <x:c r="I5" s="17" t="str">
-        <x:v>하이트진로㈜(HiteJinro Co., Ltd.)은 대한민국에서 운영되는 대한민국의 희석식·증류식 소주 제조사입니다. 1924년 설립 또는 계승 연혁을 기준으로 하며, 공개 자료에서 참이슬·진로·일품진로의 제조사로 확인됩니다. 2026.05.26 국세청 K-SUUL 참가 제품(참이슬·일품진로) 확인</x:v>
+        <x:v>하이트진로㈜(HiteJinro Co., Ltd.)는 1924년 진천양조상회에서 출발한 대한민국의 종합 주류 기업입니다. 참이슬과 진로를 중심으로 대중적인 희석식 소주를 전개하고, 일품진로를 통해 증류식 소주 제품군도 운영합니다. 소주와 맥주를 함께 다루는 폭넓은 포트폴리오와 전국 단위 생산·유통 기반이 특징입니다.</x:v>
       </x:c>
       <x:c r="J5" s="17" t="str">
-        <x:v>하이트진로㈜ (HiteJinro Co., Ltd.) is a diluted and distilled soju producer operating in South Korea. Its public history is traced to 1924. Public sources identify it as the producer of 참이슬·진로·일품진로. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>HiteJinro Co., Ltd. is a Korean drinks company whose history begins with Jincheon Brewery in 1924. Its soju portfolio combines mainstream diluted brands such as Chamisul and Jinro with distilled expressions led by Ilpoom Jinro. A nationwide production and distribution base, together with a broad portfolio spanning both soju and beer, defines the company’s scale and identity.</x:v>
       </x:c>
       <x:c r="K5" s="17" t="str">
         <x:v>참이슬, 진로, 일품진로</x:v>
@@ -1056,10 +1056,10 @@
       </x:c>
       <x:c r="H6" s="17" t="str"/>
       <x:c r="I6" s="17" t="str">
-        <x:v>롯데칠성음료㈜(LOTTE Chilsung Beverage Co., Ltd.)은 대한민국에서 운영되는 대한민국의 희석식·증류식 소주 제조사입니다. 1950년 설립 또는 계승 연혁을 기준으로 하며, 공개 자료에서 처음처럼·새로·대장부의 제조사로 확인됩니다. 2026.05.26 국세청 K-SUUL 참가 제품(새로) 및 공식 회사 자료 확인</x:v>
+        <x:v>롯데칠성음료㈜(LOTTE Chilsung Beverage Co., Ltd.)는 1950년 설립된 음료·주류 기업입니다. 처음처럼과 새로를 중심으로 희석식 소주를 전개하며, 대장부 등 증류식 소주 제품도 함께 다룹니다. 음료 사업에서 축적한 전국 유통망과 다양한 주류 카테고리를 결합한 종합 포트폴리오가 특징입니다.</x:v>
       </x:c>
       <x:c r="J6" s="17" t="str">
-        <x:v>롯데칠성음료㈜ (LOTTE Chilsung Beverage Co., Ltd.) is a diluted and distilled soju producer operating in South Korea. Its public history is traced to 1950. Public sources identify it as the producer of 처음처럼·새로·대장부. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>LOTTE Chilsung Beverage Co., Ltd. is a Korean beverage and alcoholic-drinks company founded in 1950. Its soju range is led by diluted brands such as Chum Churum and Saero, alongside distilled products including Daejangbu. The company is distinguished by a nationwide distribution network and a broad portfolio that combines soft drinks with several alcoholic-drinks categories.</x:v>
       </x:c>
       <x:c r="K6" s="17" t="str">
         <x:v>처음처럼, 새로, 대장부</x:v>
@@ -1118,10 +1118,10 @@
         <x:v>경상남도</x:v>
       </x:c>
       <x:c r="I7" s="17" t="str">
-        <x:v>㈜무학(Muhak Co., Ltd.)은 경상남도에 기반을 둔 대한민국의 희석식 소주 제조사입니다. 1929년 설립 또는 계승 연혁을 기준으로 하며, 공개 자료에서 좋은데이·화이트의 제조사로 확인됩니다. 2026.03.09 공식 좋은데이 리뉴얼 출시 자료와 2026 국세청 참가 명단 확인</x:v>
+        <x:v>㈜무학(Muhak Co., Ltd.)은 1929년부터 이어진 경상남도 기반의 주류 기업입니다. 좋은데이와 화이트를 중심으로 희석식 소주를 생산하며, 부산·울산·경남을 비롯한 영남권에서 오랫동안 지역 브랜드 정체성을 쌓아 왔습니다. 부드러운 음용성을 지향하는 저도 소주 제품군을 지속적으로 발전시킨 점이 특징입니다.</x:v>
       </x:c>
       <x:c r="J7" s="17" t="str">
-        <x:v>㈜무학 (Muhak Co., Ltd.) is a diluted soju producer based in Gyeongsangnam-do, South Korea. Its public history is traced to 1929. Public sources identify it as the producer of 좋은데이·화이트. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>Muhak Co., Ltd. is a Gyeongsangnam-do-based drinks company with a history dating to 1929. It produces diluted soju led by Good Day and White and has built a long-standing regional identity across southeastern Korea. Its portfolio is particularly associated with lower-strength soju designed for a softer drinking style.</x:v>
       </x:c>
       <x:c r="K7" s="17" t="str">
         <x:v>좋은데이, 화이트</x:v>
@@ -1180,10 +1180,10 @@
         <x:v>부산</x:v>
       </x:c>
       <x:c r="I8" s="17" t="str">
-        <x:v>대선주조㈜(Daesun Distilling Co., Ltd.)은 부산에 기반을 둔 대한민국의 희석식 소주 제조사입니다. 1930년 설립 또는 계승 연혁을 기준으로 하며, 공개 자료에서 대선·C1·대선 샤인머스캣의 제조사로 확인됩니다. 2026.05.26 국세청 K-SUUL 참가 제품(대선) 확인</x:v>
+        <x:v>대선주조㈜(Daesun Distilling Co., Ltd.)은 1930년 설립된 부산 기반의 소주 제조사입니다. 대선과 C1을 중심으로 희석식 소주를 생산하고, 부산 지역의 식문화와 유통망에 밀착한 브랜드 운영을 이어 왔습니다. 지역 대표 소주와 계절·향미형 파생 제품을 함께 전개하는 구성이 특징입니다.</x:v>
       </x:c>
       <x:c r="J8" s="17" t="str">
-        <x:v>대선주조㈜ (Daesun Distilling Co., Ltd.) is a diluted soju producer based in Busan, South Korea. Its public history is traced to 1930. Public sources identify it as the producer of 대선·C1·대선 샤인머스캣. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>Daesun Distilling Co., Ltd. is a Busan-based soju producer founded in 1930. Its diluted-soju portfolio is led by Daesun and C1, supported by a brand and distribution presence closely tied to Busan’s local drinking culture. The range combines its core regional labels with seasonal and flavour-led extensions.</x:v>
       </x:c>
       <x:c r="K8" s="17" t="str">
         <x:v>대선, C1, 대선 샤인머스캣</x:v>
@@ -1242,10 +1242,10 @@
         <x:v>전라남도</x:v>
       </x:c>
       <x:c r="I9" s="17" t="str">
-        <x:v>보해양조㈜(Bohae Brewery Co., Ltd.)은 전라남도에 기반을 둔 대한민국의 희석식 소주 제조사입니다. 1950년 설립 또는 계승 연혁을 기준으로 하며, 공개 자료에서 잎새주·보해골드의 제조사로 확인됩니다. 2025년 잎새주 제품 운영 자료와 국세청 국내주류 제품 목록 교차 확인</x:v>
+        <x:v>보해양조㈜(Bohae Brewery Co., Ltd.)은 1950년 설립된 전라남도 기반의 주류 기업입니다. 잎새주와 보해골드를 중심으로 희석식 소주를 생산하며, 광주·전남을 중심으로 형성된 지역 브랜드 기반을 갖고 있습니다. 소주뿐 아니라 과실주와 전통주까지 폭넓게 다루는 종합 양조 역량이 특징입니다.</x:v>
       </x:c>
       <x:c r="J9" s="17" t="str">
-        <x:v>보해양조㈜ (Bohae Brewery Co., Ltd.) is a diluted soju producer based in Jeollanam-do, South Korea. Its public history is traced to 1950. Public sources identify it as the producer of 잎새주·보해골드. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>Bohae Brewery Co., Ltd. is a Jeollanam-do-based drinks producer founded in 1950. Its diluted-soju range is led by Ipseju and Bohae Gold, supported by a strong regional base in Gwangju and Jeollanam-do. The company’s production capability extends beyond soju to fruit wines and traditional Korean alcoholic drinks.</x:v>
       </x:c>
       <x:c r="K9" s="17" t="str">
         <x:v>잎새주, 보해골드</x:v>
@@ -1304,10 +1304,10 @@
         <x:v>대구</x:v>
       </x:c>
       <x:c r="I10" s="17" t="str">
-        <x:v>㈜금복주(Kumbokju Co., Ltd.)은 대구에 기반을 둔 대한민국의 희석식·증류식 소주 제조사입니다. 1957년 설립 또는 계승 연혁을 기준으로 하며, 공개 자료에서 참소주·제로투·제왕 안동소주의 제조사로 확인됩니다. 2026.08 참소주 리뉴얼 판매 보도와 공식 회사 사이트 확인</x:v>
+        <x:v>㈜금복주(Kumbokju Co., Ltd.)는 1957년 설립된 대구 기반의 주류 기업입니다. 참소주와 제로투 같은 희석식 소주를 중심으로 대구·경북 지역의 대표 브랜드를 운영하며, 제왕 안동소주를 통해 증류식 소주도 함께 전개합니다. 지역 대중주와 전통 증류주를 한 포트폴리오에서 다루는 점이 특징입니다.</x:v>
       </x:c>
       <x:c r="J10" s="17" t="str">
-        <x:v>㈜금복주 (Kumbokju Co., Ltd.) is a diluted and distilled soju producer based in Daegu, South Korea. Its public history is traced to 1957. Public sources identify it as the producer of 참소주·제로투·제왕 안동소주. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>Kumbokju Co., Ltd. is a Daegu-based drinks company founded in 1957. It operates major diluted-soju brands in Daegu and Gyeongsangbuk-do, including Cham Soju and Zero2, while also producing distilled soju through the Jewang Andong Soju range. Its portfolio links a strong regional mainstream business with traditional distilled expressions.</x:v>
       </x:c>
       <x:c r="K10" s="17" t="str">
         <x:v>참소주, 제로투, 제왕 안동소주</x:v>
@@ -1366,10 +1366,10 @@
         <x:v>대전</x:v>
       </x:c>
       <x:c r="I11" s="17" t="str">
-        <x:v>㈜선양소주(Sunyang Soju Co., Ltd.)은 대전에 기반을 둔 대한민국의 희석식·증류식 소주 제조사입니다. 1973년 설립 또는 계승 연혁을 기준으로 하며, 공개 자료에서 선양·선양린·사락 GOLD의 제조사로 확인됩니다. 2026.05.26 국세청 K-SUUL 참가 제품(사락 GOLD) 확인</x:v>
+        <x:v>㈜선양소주(Sunyang Soju Co., Ltd.)는 1973년 선양주조에서 출발한 대전·충청권 기반의 소주 제조사입니다. 선양과 선양린을 중심으로 희석식 소주를 생산하고, 사락 GOLD 같은 증류식 소주도 함께 선보입니다. 지역 밀착형 대중 소주와 프리미엄 증류 제품을 병행하는 구성이 특징입니다.</x:v>
       </x:c>
       <x:c r="J11" s="17" t="str">
-        <x:v>㈜선양소주 (Sunyang Soju Co., Ltd.) is a diluted and distilled soju producer based in Daejeon, South Korea. Its public history is traced to 1973. Public sources identify it as the producer of 선양·선양린·사락 GOLD. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>Sunyang Soju Co., Ltd. traces its history to Sunyang Brewery, established in 1973, and is rooted in Daejeon and the Chungcheong region. Its range combines diluted soju led by Sunyang and Sunyang Linn with distilled expressions such as S-arak GOLD. The company’s identity joins a locally focused mainstream business with a smaller premium distilled portfolio.</x:v>
       </x:c>
       <x:c r="K11" s="17" t="str">
         <x:v>선양, 선양린, 사락 GOLD</x:v>
@@ -1428,10 +1428,10 @@
         <x:v>충청북도</x:v>
       </x:c>
       <x:c r="I12" s="17" t="str">
-        <x:v>㈜충북소주(Chungbuk Soju Co., Ltd.)은 충청북도에 기반을 둔 대한민국의 희석식 소주 제조사입니다. 1957년 설립 또는 계승 연혁을 기준으로 하며, 공개 자료에서 시원한 청풍·맑은바람의 제조사로 확인됩니다. 2026년 기업 활동 자료와 국세청 제품 목록 확인. 공식 사이트는 조사 시점 접속 불가</x:v>
+        <x:v>㈜충북소주(Chungbuk Soju Co., Ltd.)는 충청북도를 기반으로 시원한 청풍과 맑은바람을 생산하는 희석식 소주 제조사입니다. 1957년부터 이어진 지역 소주의 계보를 바탕으로 충북 지역의 유통과 소비 문화에 밀착한 제품을 운영해 왔습니다. 지역명과 청정 이미지를 전면에 둔 브랜드 정체성이 특징입니다.</x:v>
       </x:c>
       <x:c r="J12" s="17" t="str">
-        <x:v>㈜충북소주 (Chungbuk Soju Co., Ltd.) is a diluted soju producer based in Chungcheongbuk-do, South Korea. Its public history is traced to 1957. Public sources identify it as the producer of 시원한 청풍·맑은바람. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>Chungbuk Soju Co., Ltd. is a diluted-soju producer based in Chungcheongbuk-do, with Cool Cheongpung and Malgeun Baram as its core brands. Drawing on a regional soju lineage that dates to 1957, it has developed products closely tied to local distribution and drinking culture. Its brand identity places strong emphasis on Chungcheongbuk-do and a clean, fresh image.</x:v>
       </x:c>
       <x:c r="K12" s="17" t="str">
         <x:v>시원한 청풍, 맑은바람</x:v>
@@ -1490,10 +1490,10 @@
         <x:v>제주도</x:v>
       </x:c>
       <x:c r="I13" s="17" t="str">
-        <x:v>㈜한라산(Hallasan Co., Ltd.)은 제주도에 기반을 둔 대한민국의 희석식 소주 제조사입니다. 1950년 설립 또는 계승 연혁을 기준으로 하며, 공개 자료에서 한라산·한라산 순한의 제조사로 확인됩니다. 2026.05.26 국세청 K-SUUL 참가 제품(한라산) 확인</x:v>
+        <x:v>㈜한라산(Hallasan Co., Ltd.)은 1950년 호남양조장에서 출발한 제주도의 소주 제조사입니다. 한라산과 한라산 순한을 중심으로 희석식 소주를 생산하며, 제주 화산암반수와 제주 현지 생산을 브랜드 정체성의 핵심으로 삼고 있습니다. 섬 지역의 독립적인 생산 기반과 지역 대표성이 특징입니다.</x:v>
       </x:c>
       <x:c r="J13" s="17" t="str">
-        <x:v>㈜한라산 (Hallasan Co., Ltd.) is a diluted soju producer based in Jeju-do, South Korea. Its public history is traced to 1950. Public sources identify it as the producer of 한라산·한라산 순한. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>Hallasan Co., Ltd. is a Jeju-do soju producer whose history begins with Honam Brewery in 1950. Its diluted-soju portfolio is led by Hallasan and Hallasan Mild, with Jeju volcanic bedrock water and local production forming central parts of the brand identity. An independent island production base and strong regional representation distinguish the company.</x:v>
       </x:c>
       <x:c r="K13" s="17" t="str">
         <x:v>한라산, 한라산 순한</x:v>
@@ -1550,10 +1550,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I14" s="17" t="str">
-        <x:v>㈜배혜정농업회사법인(Bae Hye Jeong Agricultural Corporation)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 로아 포르토·우곡소주·로아19화이트·로아19옐로우·로아19레드·로아40화이트·로아40퍼플의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>㈜배혜정농업회사법인(Bae Hye Jeong Agricultural Corporation)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 로아 포르토·우곡소주·로아19화이트·로아19옐로우·로아19레드·로아40화이트·로아40퍼플 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J14" s="17" t="str">
-        <x:v>㈜배혜정농업회사법인 (Bae Hye Jeong Agricultural Corporation) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 로아 포르토·우곡소주·로아19화이트·로아19옐로우·로아19레드·로아40화이트·로아40퍼플. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>㈜배혜정농업회사법인 (Bae Hye Jeong Agricultural Corporation) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 로아 포르토, 우곡소주, 로아19화이트, 로아19옐로우, 로아19레드, 로아40화이트, 로아40퍼플. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K14" s="17" t="str">
         <x:v>로아 포르토, 우곡소주, 로아19화이트, 로아19옐로우, 로아19레드, 로아40화이트, 로아40퍼플</x:v>
@@ -1608,10 +1608,10 @@
         <x:v>충청남도</x:v>
       </x:c>
       <x:c r="I15" s="17" t="str">
-        <x:v>㈜백제명가주조(Baekjemyeonggajujo Brewery)은 충청남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 백제한산군주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>㈜백제명가주조(Baekjemyeonggajujo Brewery)은 대한민국 충청남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 백제한산군주 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J15" s="17" t="str">
-        <x:v>㈜백제명가주조 (Baekjemyeonggajujo Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Public sources identify it as the producer of 백제한산군주. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>㈜백제명가주조 (Baekjemyeonggajujo Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Its core range includes 백제한산군주. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K15" s="17" t="str">
         <x:v>백제한산군주</x:v>
@@ -1666,10 +1666,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I16" s="17" t="str">
-        <x:v>㈜우보주책(Ubojuchaek Brewery)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 양평 밀 소주의 제조사로 확인됩니다. 공개 제품 설명에는 밀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>㈜우보주책(Ubojuchaek Brewery)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 양평 밀 소주 등이 포함됩니다. 제품 원료에는 밀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J16" s="17" t="str">
-        <x:v>㈜우보주책 (Ubojuchaek Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 양평 밀 소주. Published product information refers to ingredients including 밀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>㈜우보주책 (Ubojuchaek Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 양평 밀 소주. The range uses ingredients such as wheat. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K16" s="17" t="str">
         <x:v>양평 밀 소주</x:v>
@@ -1724,10 +1724,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I17" s="17" t="str">
-        <x:v>㈜좋은술(Joeunsul Co., Ltd.)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 천비향 화주의 제조사로 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>㈜좋은술(Joeunsul Co., Ltd.)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 천비향 화주 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J17" s="17" t="str">
-        <x:v>㈜좋은술 (Joeunsul Co., Ltd.) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 천비향 화주. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>㈜좋은술 (Joeunsul Co., Ltd.) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 천비향 화주. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K17" s="17" t="str">
         <x:v>천비향 화주</x:v>
@@ -1784,10 +1784,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I18" s="17" t="str">
-        <x:v>㈜화요(Hwayo Co., Ltd.)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 화요 41%, 25%, 17%·화요53·화요41·화요25·화요 X.Premium·화요17의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>㈜화요(Hwayo Co., Ltd.)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 화요 41%, 25%, 17%·화요53·화요41·화요25·화요 X.Premium·화요17 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J18" s="17" t="str">
-        <x:v>㈜화요 (Hwayo Co., Ltd.) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 화요 41%, 25%, 17%·화요53·화요41·화요25·화요 X.Premium·화요17. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>㈜화요 (Hwayo Co., Ltd.) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 화요 41%, 25%, 17%, 화요53, 화요41, 화요25, 화요 X.Premium, 화요17. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K18" s="17" t="str">
         <x:v>화요 41%, 25%, 17%, 화요53, 화요41, 화요25, 화요 X.Premium, 화요17</x:v>
@@ -1844,10 +1844,10 @@
         <x:v>경상북도</x:v>
       </x:c>
       <x:c r="I19" s="17" t="str">
-        <x:v>국가유산·명인 조옥화 안동소주(Cho Ok-hwa Andong Soju)은 경상북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 국가유산·명인 조옥화 안동소주 45도의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>국가유산·명인 조옥화 안동소주(Cho Ok-hwa Andong Soju)은 대한민국 경상북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 국가유산·명인 조옥화 안동소주 45도 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J19" s="17" t="str">
-        <x:v>국가유산·명인 조옥화 안동소주 (Cho Ok-hwa Andong Soju) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Public sources identify it as the producer of 국가유산·명인 조옥화 안동소주 45도. Published product information refers to ingredients including 쌀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>국가유산·명인 조옥화 안동소주 (Cho Ok-hwa Andong Soju) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Its core range includes 국가유산·명인 조옥화 안동소주 45도. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K19" s="17" t="str">
         <x:v>국가유산·명인 조옥화 안동소주 45도</x:v>
@@ -1902,10 +1902,10 @@
         <x:v>강원도</x:v>
       </x:c>
       <x:c r="I20" s="17" t="str">
-        <x:v>국순당 횡성양조장(Kooksoondang Hoengseong Brewery)은 강원도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 려·려 2013 본의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·고구마 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>국순당 횡성양조장(Kooksoondang Hoengseong Brewery)은 대한민국 강원도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 려·려 2013 본 등이 포함됩니다. 제품 원료에는 쌀·고구마 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J20" s="17" t="str">
-        <x:v>국순당 횡성양조장 (Kooksoondang Hoengseong Brewery) is a distilled soju producer based in Gangwon-do, South Korea. Public sources identify it as the producer of 려·려 2013 본. Published product information refers to ingredients including 쌀·고구마. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>국순당 횡성양조장 (Kooksoondang Hoengseong Brewery) is a distilled soju producer based in Gangwon-do, South Korea. Its core range includes 려, 려 2013 본. The range uses ingredients such as rice, sweet potato. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K20" s="17" t="str">
         <x:v>려, 려 2013 본</x:v>
@@ -1960,10 +1960,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I21" s="17" t="str">
-        <x:v>국순당여주명주㈜(Kooksoondang Yeoju Myungju Co., Ltd.)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 려 고구마 소주·려40의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·고구마 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>국순당여주명주㈜(Kooksoondang Yeoju Myungju Co., Ltd.)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 려 고구마 소주·려40 등이 포함됩니다. 제품 원료에는 쌀·고구마 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J21" s="17" t="str">
-        <x:v>국순당여주명주㈜ (Kooksoondang Yeoju Myungju Co., Ltd.) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 려 고구마 소주·려40. Published product information refers to ingredients including 쌀·고구마. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>국순당여주명주㈜ (Kooksoondang Yeoju Myungju Co., Ltd.) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 려 고구마 소주, 려40. The range uses ingredients such as rice, sweet potato. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K21" s="17" t="str">
         <x:v>려 고구마 소주, 려40</x:v>
@@ -2020,10 +2020,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I22" s="17" t="str">
-        <x:v>남한산성소주(Namhansanseongsoju Brewery)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 남한산성소주·남한산성소주 21의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·보리·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>남한산성소주(Namhansanseongsoju Brewery)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 남한산성소주·남한산성소주 21 등이 포함됩니다. 제품 원료에는 쌀·보리·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J22" s="17" t="str">
-        <x:v>남한산성소주 (Namhansanseongsoju Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 남한산성소주·남한산성소주 21. Published product information refers to ingredients including 쌀·보리·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>남한산성소주 (Namhansanseongsoju Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 남한산성소주, 남한산성소주 21. The range uses ingredients such as rice, barley, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K22" s="17" t="str">
         <x:v>남한산성소주, 남한산성소주 21</x:v>
@@ -2078,10 +2078,10 @@
         <x:v>전라북도</x:v>
       </x:c>
       <x:c r="I23" s="17" t="str">
-        <x:v>내변산(Naebyeonsan Brewery)은 전라북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 백제소주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>내변산(Naebyeonsan Brewery)은 대한민국 전라북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 백제소주 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J23" s="17" t="str">
-        <x:v>내변산 (Naebyeonsan Brewery) is a distilled soju producer based in Jeollabuk-do, South Korea. Public sources identify it as the producer of 백제소주. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>내변산 (Naebyeonsan Brewery) is a distilled soju producer based in Jeollabuk-do, South Korea. Its core range includes 백제소주. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K23" s="17" t="str">
         <x:v>백제소주</x:v>
@@ -2132,10 +2132,10 @@
       </x:c>
       <x:c r="H24" s="17" t="str"/>
       <x:c r="I24" s="17" t="str">
-        <x:v>내외 디스틸러리(Naeoe Distillery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 내외39의 제조사로 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>내외 디스틸러리(Naeoe Distillery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 내외39 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J24" s="17" t="str">
-        <x:v>내외 디스틸러리 (Naeoe Distillery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 내외39. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>내외 디스틸러리 (Naeoe Distillery) is a distilled soju producer operating in South Korea. Its core range includes 내외39. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K24" s="17" t="str">
         <x:v>내외39</x:v>
@@ -2188,10 +2188,10 @@
         <x:v>충청남도</x:v>
       </x:c>
       <x:c r="I25" s="17" t="str">
-        <x:v>농업회사법인 (유) 양촌양조(Yangchonyangjo Brewery)은 충청남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 여유40의 제조사로 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>농업회사법인 (유) 양촌양조(Yangchonyangjo Brewery)은 대한민국 충청남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 여유40 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J25" s="17" t="str">
-        <x:v>농업회사법인 (유) 양촌양조 (Yangchonyangjo Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Public sources identify it as the producer of 여유40. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>농업회사법인 (유) 양촌양조 (Yangchonyangjo Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Its core range includes 여유40. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K25" s="17" t="str">
         <x:v>여유40</x:v>
@@ -2244,10 +2244,10 @@
         <x:v>충청북도</x:v>
       </x:c>
       <x:c r="I26" s="17" t="str">
-        <x:v>농업회사법인 (유) 화양(Hwayang Agricultural Corporation)은 충청북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 풍정사계 동의 제조사로 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>농업회사법인 (유) 화양(Hwayang Agricultural Corporation)은 대한민국 충청북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 풍정사계 동 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J26" s="17" t="str">
-        <x:v>농업회사법인 (유) 화양 (Hwayang Agricultural Corporation) is a distilled soju producer based in Chungcheongbuk-do, South Korea. Public sources identify it as the producer of 풍정사계 동. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>농업회사법인 (유) 화양 (Hwayang Agricultural Corporation) is a distilled soju producer based in Chungcheongbuk-do, South Korea. Its core range includes 풍정사계 동. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K26" s="17" t="str">
         <x:v>풍정사계 동</x:v>
@@ -2304,10 +2304,10 @@
         <x:v>강원도</x:v>
       </x:c>
       <x:c r="I27" s="17" t="str">
-        <x:v>농업회사법인 ㈜달홀주조(Dalholjujo Brewery)은 강원도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 달홀진주25·달홀진주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>농업회사법인 ㈜달홀주조(Dalholjujo Brewery)은 대한민국 강원도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 달홀진주25·달홀진주 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J27" s="17" t="str">
-        <x:v>농업회사법인 ㈜달홀주조 (Dalholjujo Brewery) is a distilled soju producer based in Gangwon-do, South Korea. Public sources identify it as the producer of 달홀진주25·달홀진주. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>농업회사법인 ㈜달홀주조 (Dalholjujo Brewery) is a distilled soju producer based in Gangwon-do, South Korea. Its core range includes 달홀진주25, 달홀진주. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K27" s="17" t="str">
         <x:v>달홀진주25, 달홀진주</x:v>
@@ -2364,10 +2364,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I28" s="17" t="str">
-        <x:v>농업회사법인 ㈜온증류소(Distillery On Co., Ltd.)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 형형 25·연연 25·형형40의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>농업회사법인 ㈜온증류소(Distillery On Co., Ltd.)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 형형 25·연연 25·형형40 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J28" s="17" t="str">
-        <x:v>농업회사법인 ㈜온증류소 (Distillery On Co., Ltd.) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 형형 25·연연 25·형형40. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>농업회사법인 ㈜온증류소 (Distillery On Co., Ltd.) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 형형 25, 연연 25, 형형40. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K28" s="17" t="str">
         <x:v>형형 25, 연연 25, 형형40</x:v>
@@ -2422,10 +2422,10 @@
         <x:v>충청북도</x:v>
       </x:c>
       <x:c r="I29" s="17" t="str">
-        <x:v>농업회사법인 담을(Dameul Brewery)은 충청북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 주향소주 25·주향담을·주향이오·주향아라·주향아라 스페셜·이음주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>농업회사법인 담을(Dameul Brewery)은 대한민국 충청북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 주향소주 25·주향담을·주향이오·주향아라·주향아라 스페셜·이음주 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J29" s="17" t="str">
-        <x:v>농업회사법인 담을 (Dameul Brewery) is a distilled soju producer based in Chungcheongbuk-do, South Korea. Public sources identify it as the producer of 주향소주 25·주향담을·주향이오·주향아라·주향아라 스페셜·이음주. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>농업회사법인 담을 (Dameul Brewery) is a distilled soju producer based in Chungcheongbuk-do, South Korea. Its core range includes 주향소주 25, 주향담을, 주향이오, 주향아라, 주향아라 스페셜, 이음주. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K29" s="17" t="str">
         <x:v>주향소주 25, 주향담을, 주향이오, 주향아라, 주향아라 스페셜, 이음주</x:v>
@@ -2482,10 +2482,10 @@
         <x:v>충청남도</x:v>
       </x:c>
       <x:c r="I30" s="17" t="str">
-        <x:v>농업회사법인 아리랑주조㈜(Arirangjujo Brewery)은 충청남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 겨울소주 25·겨울소주45의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>농업회사법인 아리랑주조㈜(Arirangjujo Brewery)은 대한민국 충청남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 겨울소주 25·겨울소주45 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J30" s="17" t="str">
-        <x:v>농업회사법인 아리랑주조㈜ (Arirangjujo Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Public sources identify it as the producer of 겨울소주 25·겨울소주45. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>농업회사법인 아리랑주조㈜ (Arirangjujo Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Its core range includes 겨울소주 25, 겨울소주45. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K30" s="17" t="str">
         <x:v>겨울소주 25, 겨울소주45</x:v>
@@ -2540,10 +2540,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I31" s="17" t="str">
-        <x:v>농업회사법인 연천양조㈜(Yeoncheonyangjo Brewery)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 연천 우주·연천우주 38의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>농업회사법인 연천양조㈜(Yeoncheonyangjo Brewery)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 연천 우주·연천우주 38 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J31" s="17" t="str">
-        <x:v>농업회사법인 연천양조㈜ (Yeoncheonyangjo Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 연천 우주·연천우주 38. Published product information refers to ingredients including 쌀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>농업회사법인 연천양조㈜ (Yeoncheonyangjo Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 연천 우주, 연천우주 38. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K31" s="17" t="str">
         <x:v>연천 우주, 연천우주 38</x:v>
@@ -2598,10 +2598,10 @@
         <x:v>충청남도</x:v>
       </x:c>
       <x:c r="I32" s="17" t="str">
-        <x:v>농업회사법인 이가수불㈜(Igasubul Brewery)은 충청남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 이상헌 소주의 제조사로 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>농업회사법인 이가수불㈜(Igasubul Brewery)은 대한민국 충청남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 이상헌 소주 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J32" s="17" t="str">
-        <x:v>농업회사법인 이가수불㈜ (Igasubul Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Public sources identify it as the producer of 이상헌 소주. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>농업회사법인 이가수불㈜ (Igasubul Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Its core range includes 이상헌 소주. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K32" s="17" t="str">
         <x:v>이상헌 소주</x:v>
@@ -2656,10 +2656,10 @@
         <x:v>충청북도</x:v>
       </x:c>
       <x:c r="I33" s="17" t="str">
-        <x:v>농업회사법인 주식회사 다농바이오(Danongbaio Brewery)은 충청북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 가무치 25도의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>농업회사법인 주식회사 다농바이오(Danongbaio Brewery)은 대한민국 충청북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 가무치 25도 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J33" s="17" t="str">
-        <x:v>농업회사법인 주식회사 다농바이오 (Danongbaio Brewery) is a distilled soju producer based in Chungcheongbuk-do, South Korea. Public sources identify it as the producer of 가무치 25도. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>농업회사법인 주식회사 다농바이오 (Danongbaio Brewery) is a distilled soju producer based in Chungcheongbuk-do, South Korea. Its core range includes 가무치 25도. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K33" s="17" t="str">
         <x:v>가무치 25도</x:v>
@@ -2714,10 +2714,10 @@
         <x:v>인천</x:v>
       </x:c>
       <x:c r="I34" s="17" t="str">
-        <x:v>농업회사법인 주식회사 주연향(Juyeonhyang Brewery)은 인천에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 야수 S 53의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·고구마 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>농업회사법인 주식회사 주연향(Juyeonhyang Brewery)은 대한민국 인천에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 야수 S 53 등이 포함됩니다. 제품 원료에는 쌀·고구마 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J34" s="17" t="str">
-        <x:v>농업회사법인 주식회사 주연향 (Juyeonhyang Brewery) is a distilled soju producer based in Incheon, South Korea. Public sources identify it as the producer of 야수 S 53. Published product information refers to ingredients including 쌀·고구마. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>농업회사법인 주식회사 주연향 (Juyeonhyang Brewery) is a distilled soju producer based in Incheon, South Korea. Its core range includes 야수 S 53. The range uses ingredients such as rice, sweet potato. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K34" s="17" t="str">
         <x:v>야수 S 53</x:v>
@@ -2772,10 +2772,10 @@
         <x:v>충청북도</x:v>
       </x:c>
       <x:c r="I35" s="17" t="str">
-        <x:v>농업회사법인 토끼소주㈜(Tokki Soju Co., Ltd.)은 충청북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 토끼소주 블랙·선비 보드카의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>농업회사법인 토끼소주㈜(Tokki Soju Co., Ltd.)은 대한민국 충청북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 토끼소주 블랙·선비 보드카 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J35" s="17" t="str">
-        <x:v>농업회사법인 토끼소주㈜ (Tokki Soju Co., Ltd.) is a distilled soju producer based in Chungcheongbuk-do, South Korea. Public sources identify it as the producer of 토끼소주 블랙·선비 보드카. Published product information refers to ingredients including 쌀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>농업회사법인 토끼소주㈜ (Tokki Soju Co., Ltd.) is a distilled soju producer based in Chungcheongbuk-do, South Korea. Its core range includes 토끼소주 블랙, 선비 보드카. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K35" s="17" t="str">
         <x:v>토끼소주 블랙, 선비 보드카</x:v>
@@ -2830,10 +2830,10 @@
         <x:v>강원도</x:v>
       </x:c>
       <x:c r="I36" s="17" t="str">
-        <x:v>대작영농조합법인(Daejak Brewery)은 강원도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 모을동주 소주·모을동주소주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·밀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>대작영농조합법인(Daejak Brewery)은 대한민국 강원도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 모을동주 소주·모을동주소주 등이 포함됩니다. 제품 원료에는 쌀·밀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J36" s="17" t="str">
-        <x:v>대작영농조합법인 (Daejak Brewery) is a distilled soju producer based in Gangwon-do, South Korea. Public sources identify it as the producer of 모을동주 소주·모을동주소주. Published product information refers to ingredients including 쌀·밀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>대작영농조합법인 (Daejak Brewery) is a distilled soju producer based in Gangwon-do, South Korea. Its core range includes 모을동주 소주, 모을동주소주. The range uses ingredients such as rice, wheat. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K36" s="17" t="str">
         <x:v>모을동주 소주, 모을동주소주</x:v>
@@ -2890,10 +2890,10 @@
         <x:v>경상북도</x:v>
       </x:c>
       <x:c r="I37" s="17" t="str">
-        <x:v>맹개술도가(Maenggaesuldoga Brewery)은 경상북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 안동 진맥 소주의 제조사로 확인됩니다. 공개 제품 설명에는 밀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>맹개술도가(Maenggaesuldoga Brewery)은 대한민국 경상북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 안동 진맥 소주 등이 포함됩니다. 제품 원료에는 밀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J37" s="17" t="str">
-        <x:v>맹개술도가 (Maenggaesuldoga Brewery) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Public sources identify it as the producer of 안동 진맥 소주. Published product information refers to ingredients including 밀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>맹개술도가 (Maenggaesuldoga Brewery) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Its core range includes 안동 진맥 소주. The range uses ingredients such as wheat. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K37" s="17" t="str">
         <x:v>안동 진맥 소주</x:v>
@@ -2948,10 +2948,10 @@
         <x:v>경상북도</x:v>
       </x:c>
       <x:c r="I38" s="17" t="str">
-        <x:v>명인안동소주(Master Andong Soju)은 경상북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 명인 안동소주 양반탈·명인 안동소주 22%·명인안동소주 35%·명인안동소주/22도·명인안동소주/45도의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>명인안동소주(Master Andong Soju)은 대한민국 경상북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 명인 안동소주 양반탈·명인 안동소주 22%·명인안동소주 35%·명인안동소주/22도·명인안동소주/45도 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J38" s="17" t="str">
-        <x:v>명인안동소주 (Master Andong Soju) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Public sources identify it as the producer of 명인 안동소주 양반탈·명인 안동소주 22%·명인안동소주 35%·명인안동소주/22도·명인안동소주/45도. Published product information refers to ingredients including 쌀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>명인안동소주 (Master Andong Soju) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Its core range includes 명인 안동소주 양반탈, 명인 안동소주 22%, 명인안동소주 35%, 명인안동소주/22도, 명인안동소주/45도. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K38" s="17" t="str">
         <x:v>명인 안동소주 양반탈, 명인 안동소주 22%, 명인안동소주 35%, 명인안동소주/22도, 명인안동소주/45도</x:v>
@@ -3008,10 +3008,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I39" s="17" t="str">
-        <x:v>문배주양조원(Moonbaesool Brewery)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 문배주 용상·문배술·문배술 헤리티지 40도·문배술 천향·문배술 명작·문배술 용상·문배술 호리병의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>문배주양조원(Moonbaesool Brewery)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 문배주 용상·문배술·문배술 헤리티지 40도·문배술 천향·문배술 명작·문배술 용상·문배술 호리병 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J39" s="17" t="str">
-        <x:v>문배주양조원 (Moonbaesool Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 문배주 용상·문배술·문배술 헤리티지 40도·문배술 천향·문배술 명작·문배술 용상·문배술 호리병. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>문배주양조원 (Moonbaesool Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 문배주 용상, 문배술, 문배술 헤리티지 40도, 문배술 천향, 문배술 명작, 문배술 용상, 문배술 호리병. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K39" s="17" t="str">
         <x:v>문배주 용상, 문배술, 문배술 헤리티지 40도, 문배술 천향, 문배술 명작, 문배술 용상, 문배술 호리병</x:v>
@@ -3068,10 +3068,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I40" s="17" t="str">
-        <x:v>미음넷증류소(Fourmieum Distillery)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 소주다움 45·소주다움27의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>미음넷증류소(Fourmieum Distillery)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 소주다움 45·소주다움27 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J40" s="17" t="str">
-        <x:v>미음넷증류소 (Fourmieum Distillery) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 소주다움 45·소주다움27. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>미음넷증류소 (Fourmieum Distillery) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 소주다움 45, 소주다움27. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K40" s="17" t="str">
         <x:v>소주다움 45, 소주다움27</x:v>
@@ -3126,10 +3126,10 @@
         <x:v>경상북도</x:v>
       </x:c>
       <x:c r="I41" s="17" t="str">
-        <x:v>밀과노닐다(Milgwanonilda Brewery)은 경상북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 진맥소주 오크40%·시인의 바위·진맥소주 시인의바위·진맥소주의 제조사로 확인됩니다. 공개 제품 설명에는 밀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>밀과노닐다(Milgwanonilda Brewery)은 대한민국 경상북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 진맥소주 오크40%·시인의 바위·진맥소주 시인의바위·진맥소주 등이 포함됩니다. 제품 원료에는 밀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J41" s="17" t="str">
-        <x:v>밀과노닐다 (Milgwanonilda Brewery) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Public sources identify it as the producer of 진맥소주 오크40%·시인의 바위·진맥소주 시인의바위·진맥소주. Published product information refers to ingredients including 밀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>밀과노닐다 (Milgwanonilda Brewery) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Its core range includes 진맥소주 오크40%, 시인의 바위, 진맥소주 시인의바위, 진맥소주. The range uses ingredients such as wheat. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K41" s="17" t="str">
         <x:v>진맥소주 오크40%, 시인의 바위, 진맥소주 시인의바위, 진맥소주</x:v>
@@ -3184,10 +3184,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I42" s="17" t="str">
-        <x:v>밝은세상영농조합(Balkeunsesangyeongnongjohap Brewery)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 소호의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>밝은세상영농조합(Balkeunsesangyeongnongjohap Brewery)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 소호 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J42" s="17" t="str">
-        <x:v>밝은세상영농조합 (Balkeunsesangyeongnongjohap Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 소호. Published product information refers to ingredients including 쌀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>밝은세상영농조합 (Balkeunsesangyeongnongjohap Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 소호. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K42" s="17" t="str">
         <x:v>소호</x:v>
@@ -3242,10 +3242,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I43" s="17" t="str">
-        <x:v>배상면주가(Baesangmyeonjuga Brewery)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 느린마을소주21·감아락 25의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>배상면주가(Baesangmyeonjuga Brewery)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 느린마을소주21·감아락 25 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J43" s="17" t="str">
-        <x:v>배상면주가 (Baesangmyeonjuga Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 느린마을소주21·감아락 25. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>배상면주가 (Baesangmyeonjuga Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 느린마을소주21, 감아락 25. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K43" s="17" t="str">
         <x:v>느린마을소주21, 감아락 25</x:v>
@@ -3300,10 +3300,10 @@
         <x:v>전라남도</x:v>
       </x:c>
       <x:c r="I44" s="17" t="str">
-        <x:v>병영양조장(Byeongyeongyangjojang Brewery)은 전라남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 병영소주의 제조사로 확인됩니다. 공개 제품 설명에는 보리 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>병영양조장(Byeongyeongyangjojang Brewery)은 대한민국 전라남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 병영소주 등이 포함됩니다. 제품 원료에는 보리 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J44" s="17" t="str">
-        <x:v>병영양조장 (Byeongyeongyangjojang Brewery) is a distilled soju producer based in Jeollanam-do, South Korea. Public sources identify it as the producer of 병영소주. Published product information refers to ingredients including 보리. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>병영양조장 (Byeongyeongyangjojang Brewery) is a distilled soju producer based in Jeollanam-do, South Korea. Its core range includes 병영소주. The range uses ingredients such as barley. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K44" s="17" t="str">
         <x:v>병영소주</x:v>
@@ -3360,10 +3360,10 @@
         <x:v>제주도</x:v>
       </x:c>
       <x:c r="I45" s="17" t="str">
-        <x:v>술도가제주바당(Suldogajejubadang Brewery)은 제주도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 제주낭만의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>술도가제주바당(Suldogajejubadang Brewery)은 대한민국 제주도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 제주낭만 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J45" s="17" t="str">
-        <x:v>술도가제주바당 (Suldogajejubadang Brewery) is a distilled soju producer based in Jeju-do, South Korea. Public sources identify it as the producer of 제주낭만. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>술도가제주바당 (Suldogajejubadang Brewery) is a distilled soju producer based in Jeju-do, South Korea. Its core range includes 제주낭만. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K45" s="17" t="str">
         <x:v>제주낭만</x:v>
@@ -3420,10 +3420,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I46" s="17" t="str">
-        <x:v>술샘(Soolseam)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 2012년 설립 또는 계승 연혁을 기준으로 하며, 공개 자료에서 미르·미르25·미르54의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·밀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>술샘(Soolseam)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 2012년부터 이어진 연혁을 바탕으로 대표 제품군에는 미르·미르25·미르54 등이 포함됩니다. 제품 원료에는 쌀·밀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J46" s="17" t="str">
-        <x:v>술샘 (Soolseam) is a distilled soju producer based in Gyeonggi-do, South Korea. Its public history is traced to 2012. Public sources identify it as the producer of 미르·미르25·미르54. Published product information refers to ingredients including 쌀·밀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>술샘 (Soolseam) is a distilled soju producer based in Gyeonggi-do, South Korea. Its history dates to 2012. Its core range includes 미르, 미르25, 미르54. The range uses ingredients such as rice, wheat, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K46" s="17" t="str">
         <x:v>미르, 미르25, 미르54</x:v>
@@ -3480,10 +3480,10 @@
         <x:v>경상북도</x:v>
       </x:c>
       <x:c r="I47" s="17" t="str">
-        <x:v>안동소주일품(Ilpoom Andong Soju)은 경상북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 안동소주 일품 17도·안동소주 일품 21도의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>안동소주일품(Ilpoom Andong Soju)은 대한민국 경상북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 안동소주 일품 17도·안동소주 일품 21도 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J47" s="17" t="str">
-        <x:v>안동소주일품 (Ilpoom Andong Soju) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Public sources identify it as the producer of 안동소주 일품 17도·안동소주 일품 21도. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>안동소주일품 (Ilpoom Andong Soju) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Its core range includes 안동소주 일품 17도, 안동소주 일품 21도. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K47" s="17" t="str">
         <x:v>안동소주 일품 17도, 안동소주 일품 21도</x:v>
@@ -3538,10 +3538,10 @@
         <x:v>경상북도</x:v>
       </x:c>
       <x:c r="I48" s="17" t="str">
-        <x:v>안동전통명주㈜(Andongjeontongmyeongju Brewery)은 경상북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 느낌 30·필·느낌의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>안동전통명주㈜(Andongjeontongmyeongju Brewery)은 대한민국 경상북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 느낌 30·필·느낌 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J48" s="17" t="str">
-        <x:v>안동전통명주㈜ (Andongjeontongmyeongju Brewery) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Public sources identify it as the producer of 느낌 30·필·느낌. Published product information refers to ingredients including 쌀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>안동전통명주㈜ (Andongjeontongmyeongju Brewery) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Its core range includes 느낌 30, 필, 느낌. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K48" s="17" t="str">
         <x:v>느낌 30, 필, 느낌</x:v>
@@ -3598,10 +3598,10 @@
         <x:v>경상북도</x:v>
       </x:c>
       <x:c r="I49" s="17" t="str">
-        <x:v>양반안동소주(Yangban Andong Soju)은 경상북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 양반안동소주 3년산 호리병의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>양반안동소주(Yangban Andong Soju)은 대한민국 경상북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 양반안동소주 3년산 호리병 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J49" s="17" t="str">
-        <x:v>양반안동소주 (Yangban Andong Soju) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Public sources identify it as the producer of 양반안동소주 3년산 호리병. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>양반안동소주 (Yangban Andong Soju) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Its core range includes 양반안동소주 3년산 호리병. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K49" s="17" t="str">
         <x:v>양반안동소주 3년산 호리병</x:v>
@@ -3656,10 +3656,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I50" s="17" t="str">
-        <x:v>오산양조(Osanyangjo Brewery)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 독산 53·독산 30의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>오산양조(Osanyangjo Brewery)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 독산 53·독산 30 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J50" s="17" t="str">
-        <x:v>오산양조 (Osanyangjo Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 독산 53·독산 30. Published product information refers to ingredients including 쌀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>오산양조 (Osanyangjo Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 독산 53, 독산 30. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K50" s="17" t="str">
         <x:v>독산 53, 독산 30</x:v>
@@ -3714,10 +3714,10 @@
         <x:v>충청남도</x:v>
       </x:c>
       <x:c r="I51" s="17" t="str">
-        <x:v>옥순가 소곡주 마주(Oksunga Sogokju Maju Brewery)은 충청남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 마주 소곡화주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·밀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>옥순가 소곡주 마주(Oksunga Sogokju Maju Brewery)은 대한민국 충청남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 마주 소곡화주 등이 포함됩니다. 제품 원료에는 쌀·밀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J51" s="17" t="str">
-        <x:v>옥순가 소곡주 마주 (Oksunga Sogokju Maju Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Public sources identify it as the producer of 마주 소곡화주. Published product information refers to ingredients including 쌀·밀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>옥순가 소곡주 마주 (Oksunga Sogokju Maju Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Its core range includes 마주 소곡화주. The range uses ingredients such as rice, wheat, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K51" s="17" t="str">
         <x:v>마주 소곡화주</x:v>
@@ -3772,10 +3772,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I52" s="17" t="str">
-        <x:v>우리도가(Uridoga Brewery)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 가평소주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>우리도가(Uridoga Brewery)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 가평소주 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J52" s="17" t="str">
-        <x:v>우리도가 (Uridoga Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 가평소주. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>우리도가 (Uridoga Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 가평소주. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K52" s="17" t="str">
         <x:v>가평소주</x:v>
@@ -3830,10 +3830,10 @@
         <x:v>강원도</x:v>
       </x:c>
       <x:c r="I53" s="17" t="str">
-        <x:v>원스피리츠 농업법인 주식회사(Won Spirits Agricultural Corporation)은 강원도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 원소주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>원스피리츠 농업법인 주식회사(Won Spirits Agricultural Corporation)은 대한민국 강원도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 원소주 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J53" s="17" t="str">
-        <x:v>원스피리츠 농업법인 주식회사 (Won Spirits Agricultural Corporation) is a distilled soju producer based in Gangwon-do, South Korea. Public sources identify it as the producer of 원소주. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>원스피리츠 농업법인 주식회사 (Won Spirits Agricultural Corporation) is a distilled soju producer based in Gangwon-do, South Korea. Its core range includes 원소주. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K53" s="17" t="str">
         <x:v>원소주</x:v>
@@ -3888,10 +3888,10 @@
         <x:v>충청남도</x:v>
       </x:c>
       <x:c r="I54" s="17" t="str">
-        <x:v>원조소곡주(Wonjosogokju Brewery)은 충청남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 한산 소곡화주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>원조소곡주(Wonjosogokju Brewery)은 대한민국 충청남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 한산 소곡화주 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J54" s="17" t="str">
-        <x:v>원조소곡주 (Wonjosogokju Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Public sources identify it as the producer of 한산 소곡화주. Published product information refers to ingredients including 쌀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>원조소곡주 (Wonjosogokju Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Its core range includes 한산 소곡화주. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K54" s="17" t="str">
         <x:v>한산 소곡화주</x:v>
@@ -3946,10 +3946,10 @@
         <x:v>광주</x:v>
       </x:c>
       <x:c r="I55" s="17" t="str">
-        <x:v>월광주조(Wolgwangjujo Brewery)은 광주에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 월광주 42의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>월광주조(Wolgwangjujo Brewery)은 대한민국 광주에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 월광주 42 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J55" s="17" t="str">
-        <x:v>월광주조 (Wolgwangjujo Brewery) is a distilled soju producer based in Gwangju, South Korea. Public sources identify it as the producer of 월광주 42. Published product information refers to ingredients including 쌀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>월광주조 (Wolgwangjujo Brewery) is a distilled soju producer based in Gwangju, South Korea. Its core range includes 월광주 42. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K55" s="17" t="str">
         <x:v>월광주 42</x:v>
@@ -4004,10 +4004,10 @@
         <x:v>경상북도</x:v>
       </x:c>
       <x:c r="I56" s="17" t="str">
-        <x:v>유토피아㈜(Yutopia Brewery)은 경상북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 로얄 안동소주·양반안동소주·양식주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>유토피아㈜(Yutopia Brewery)은 대한민국 경상북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 로얄 안동소주·양반안동소주·양식주 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J56" s="17" t="str">
-        <x:v>유토피아㈜ (Yutopia Brewery) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Public sources identify it as the producer of 로얄 안동소주·양반안동소주·양식주. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>유토피아㈜ (Yutopia Brewery) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Its core range includes 로얄 안동소주, 양반안동소주, 양식주. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K56" s="17" t="str">
         <x:v>로얄 안동소주, 양반안동소주, 양식주</x:v>
@@ -4060,10 +4060,10 @@
       </x:c>
       <x:c r="H57" s="17" t="str"/>
       <x:c r="I57" s="17" t="str">
-        <x:v>제이앤제이 브루어리㈜(J&amp;J Brewery Ltd.)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 청혼 Red 25의 제조사로 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>제이앤제이 브루어리㈜(J&amp;J Brewery Ltd.)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 청혼 Red 25 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J57" s="17" t="str">
-        <x:v>제이앤제이 브루어리㈜ (J&amp;J Brewery Ltd.) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 청혼 Red 25. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>제이앤제이 브루어리㈜ (J&amp;J Brewery Ltd.) is a distilled soju producer operating in South Korea. Its core range includes 청혼 Red 25. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K57" s="17" t="str">
         <x:v>청혼 Red 25</x:v>
@@ -4120,10 +4120,10 @@
         <x:v>제주도</x:v>
       </x:c>
       <x:c r="I58" s="17" t="str">
-        <x:v>제주고소리술익는집(Jeju Gosorisul Ikneunjip)은 제주도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 제주술익는집 고소리술·제주고소리술의 제조사로 확인됩니다. 공개 제품 설명에는 누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>제주고소리술익는집(Jeju Gosorisul Ikneunjip)은 대한민국 제주도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 제주술익는집 고소리술·제주고소리술 등이 포함됩니다. 제품 원료에는 누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J58" s="17" t="str">
-        <x:v>제주고소리술익는집 (Jeju Gosorisul Ikneunjip) is a distilled soju producer based in Jeju-do, South Korea. Public sources identify it as the producer of 제주술익는집 고소리술·제주고소리술. Published product information refers to ingredients including 누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>제주고소리술익는집 (Jeju Gosorisul Ikneunjip) is a distilled soju producer based in Jeju-do, South Korea. Its core range includes 제주술익는집 고소리술, 제주고소리술. The range uses ingredients such as nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K58" s="17" t="str">
         <x:v>제주술익는집 고소리술, 제주고소리술</x:v>
@@ -4180,10 +4180,10 @@
         <x:v>충청북도</x:v>
       </x:c>
       <x:c r="I59" s="17" t="str">
-        <x:v>제천한약영농조합법인(Jecheonhanyak Brewery)은 충청북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 한비 쌀소주·한비 오가피술·한비의림소주·한비쌀소주·한비소주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>제천한약영농조합법인(Jecheonhanyak Brewery)은 대한민국 충청북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 한비 쌀소주·한비 오가피술·한비의림소주·한비쌀소주·한비소주 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J59" s="17" t="str">
-        <x:v>제천한약영농조합법인 (Jecheonhanyak Brewery) is a distilled soju producer based in Chungcheongbuk-do, South Korea. Public sources identify it as the producer of 한비 쌀소주·한비 오가피술·한비의림소주·한비쌀소주·한비소주. Published product information refers to ingredients including 쌀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>제천한약영농조합법인 (Jecheonhanyak Brewery) is a distilled soju producer based in Chungcheongbuk-do, South Korea. Its core range includes 한비 쌀소주, 한비 오가피술, 한비의림소주, 한비쌀소주, 한비소주. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K59" s="17" t="str">
         <x:v>한비 쌀소주, 한비 오가피술, 한비의림소주, 한비쌀소주, 한비소주</x:v>
@@ -4240,10 +4240,10 @@
         <x:v>충청북도</x:v>
       </x:c>
       <x:c r="I60" s="17" t="str">
-        <x:v>조은술세종㈜(Joeunsul Sejong Co., Ltd.)은 충청북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 유기농 이도 32·유기농 이도 42·이도22·이도의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>조은술세종㈜(Joeunsul Sejong Co., Ltd.)은 대한민국 충청북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 유기농 이도 32·유기농 이도 42·이도22·이도 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J60" s="17" t="str">
-        <x:v>조은술세종㈜ (Joeunsul Sejong Co., Ltd.) is a distilled soju producer based in Chungcheongbuk-do, South Korea. Public sources identify it as the producer of 유기농 이도 32·유기농 이도 42·이도22·이도. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>조은술세종㈜ (Joeunsul Sejong Co., Ltd.) is a distilled soju producer based in Chungcheongbuk-do, South Korea. Its core range includes 유기농 이도 32, 유기농 이도 42, 이도22, 이도. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K60" s="17" t="str">
         <x:v>유기농 이도 32, 유기농 이도 42, 이도22, 이도</x:v>
@@ -4300,10 +4300,10 @@
         <x:v>전라남도</x:v>
       </x:c>
       <x:c r="I61" s="17" t="str">
-        <x:v>죽향도가(Jukhyangdoga Brewery)은 전라남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 대숲 맑은 담양향 Gold의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>죽향도가(Jukhyangdoga Brewery)은 대한민국 전라남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 대숲 맑은 담양향 Gold 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J61" s="17" t="str">
-        <x:v>죽향도가 (Jukhyangdoga Brewery) is a distilled soju producer based in Jeollanam-do, South Korea. Public sources identify it as the producer of 대숲 맑은 담양향 Gold. Published product information refers to ingredients including 쌀. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>죽향도가 (Jukhyangdoga Brewery) is a distilled soju producer based in Jeollanam-do, South Korea. Its core range includes 대숲 맑은 담양향 Gold. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K61" s="17" t="str">
         <x:v>대숲 맑은 담양향 Gold</x:v>
@@ -4354,10 +4354,10 @@
       </x:c>
       <x:c r="H62" s="17" t="str"/>
       <x:c r="I62" s="17" t="str">
-        <x:v>지비지 스피리츠㈜ 농업회사법인(GBG Spirits Agricultural Corporation)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 경복궁 소주40의 제조사로 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>지비지 스피리츠㈜ 농업회사법인(GBG Spirits Agricultural Corporation)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 경복궁 소주40 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J62" s="17" t="str">
-        <x:v>지비지 스피리츠㈜ 농업회사법인 (GBG Spirits Agricultural Corporation) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 경복궁 소주40. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>지비지 스피리츠㈜ 농업회사법인 (GBG Spirits Agricultural Corporation) is a distilled soju producer operating in South Korea. Its core range includes 경복궁 소주40. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K62" s="17" t="str">
         <x:v>경복궁 소주40</x:v>
@@ -4410,10 +4410,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I63" s="17" t="str">
-        <x:v>추연당(Chuyeondang Brewery)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 소여강의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>추연당(Chuyeondang Brewery)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 소여강 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J63" s="17" t="str">
-        <x:v>추연당 (Chuyeondang Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 소여강. Published product information refers to ingredients including 쌀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>추연당 (Chuyeondang Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 소여강. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K63" s="17" t="str">
         <x:v>소여강</x:v>
@@ -4468,10 +4468,10 @@
         <x:v>충청남도</x:v>
       </x:c>
       <x:c r="I64" s="17" t="str">
-        <x:v>한산소곡주(Hansansogokju Brewery)은 충청남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 불소주·화백의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·밀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>한산소곡주(Hansansogokju Brewery)은 대한민국 충청남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 불소주·화백 등이 포함됩니다. 제품 원료에는 쌀·밀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J64" s="17" t="str">
-        <x:v>한산소곡주 (Hansansogokju Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Public sources identify it as the producer of 불소주·화백. Published product information refers to ingredients including 쌀·밀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>한산소곡주 (Hansansogokju Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Its core range includes 불소주, 화백. The range uses ingredients such as rice, wheat, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K64" s="17" t="str">
         <x:v>불소주, 화백</x:v>
@@ -4526,10 +4526,10 @@
         <x:v>충청남도</x:v>
       </x:c>
       <x:c r="I65" s="17" t="str">
-        <x:v>한산예담은소곡주(Hansanyedameunsogokju Brewery)은 충청남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 한산예담은 한산소곡화주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>한산예담은소곡주(Hansanyedameunsogokju Brewery)은 대한민국 충청남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 한산예담은 한산소곡화주 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J65" s="17" t="str">
-        <x:v>한산예담은소곡주 (Hansanyedameunsogokju Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Public sources identify it as the producer of 한산예담은 한산소곡화주. Published product information refers to ingredients including 쌀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>한산예담은소곡주 (Hansanyedameunsogokju Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Its core range includes 한산예담은 한산소곡화주. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K65" s="17" t="str">
         <x:v>한산예담은 한산소곡화주</x:v>
@@ -4584,10 +4584,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I66" s="17" t="str">
-        <x:v>한주양조(Hanjuyangjo Brewery)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 한주매화·한주/25도·한주/20도·한주/35도의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·밀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>한주양조(Hanjuyangjo Brewery)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 한주매화·한주/25도·한주/20도·한주/35도 등이 포함됩니다. 제품 원료에는 쌀·밀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J66" s="17" t="str">
-        <x:v>한주양조 (Hanjuyangjo Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 한주매화·한주/25도·한주/20도·한주/35도. Published product information refers to ingredients including 쌀·밀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>한주양조 (Hanjuyangjo Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 한주매화, 한주/25도, 한주/20도, 한주/35도. The range uses ingredients such as rice, wheat, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K66" s="17" t="str">
         <x:v>한주매화, 한주/25도, 한주/20도, 한주/35도</x:v>
@@ -4644,10 +4644,10 @@
         <x:v>강원도</x:v>
       </x:c>
       <x:c r="I67" s="17" t="str">
-        <x:v>협동조합 모월(MOWOL Cooperative)은 강원도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 모월 로·모월 인·모월인의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>협동조합 모월(MOWOL Cooperative)은 대한민국 강원도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 모월 로·모월 인·모월인 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J67" s="17" t="str">
-        <x:v>협동조합 모월 (MOWOL Cooperative) is a distilled soju producer based in Gangwon-do, South Korea. Public sources identify it as the producer of 모월 로·모월 인·모월인. Published product information refers to ingredients including 쌀·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>협동조합 모월 (MOWOL Cooperative) is a distilled soju producer based in Gangwon-do, South Korea. Its core range includes 모월 로, 모월 인, 모월인. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K67" s="17" t="str">
         <x:v>모월 로, 모월 인, 모월인</x:v>
@@ -4704,10 +4704,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I68" s="17" t="str">
-        <x:v>화심주조(Hwasimjujo Brewery)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 화심소주 군고구마의 제조사로 확인됩니다. 공개 제품 설명에는 고구마 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>화심주조(Hwasimjujo Brewery)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 화심소주 군고구마 등이 포함됩니다. 제품 원료에는 고구마 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J68" s="17" t="str">
-        <x:v>화심주조 (Hwasimjujo Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 화심소주 군고구마. Published product information refers to ingredients including 고구마. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>화심주조 (Hwasimjujo Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 화심소주 군고구마. The range uses ingredients such as sweet potato. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K68" s="17" t="str">
         <x:v>화심소주 군고구마</x:v>
@@ -4762,10 +4762,10 @@
         <x:v>충청남도</x:v>
       </x:c>
       <x:c r="I69" s="17" t="str">
-        <x:v>황금보리(유)농업회사법인(Hwanggeumbori Brewery)은 충청남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 황금보리 증류주 25·황금보리주/40도·황금보리주/25도·황금보리주/17도의 제조사로 확인됩니다. 공개 제품 설명에는 보리·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 2026년 조사 시점에 공공 카탈로그와 별도 제조사·판매 경로를 대조해 제품 활동을 확인했습니다.</x:v>
+        <x:v>황금보리(유)농업회사법인(Hwanggeumbori Brewery)은 대한민국 충청남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 황금보리 증류주 25·황금보리주/40도·황금보리주/25도·황금보리주/17도 등이 포함됩니다. 제품 원료에는 보리·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J69" s="17" t="str">
-        <x:v>황금보리(유)농업회사법인 (Hwanggeumbori Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Public sources identify it as the producer of 황금보리 증류주 25·황금보리주/40도·황금보리주/25도·황금보리주/17도. Published product information refers to ingredients including 보리·누룩·국. The producer and its soju activity were cross-checked against public and independent producer, sales, or government sources during the 2026 review.</x:v>
+        <x:v>황금보리(유)농업회사법인 (Hwanggeumbori Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Its core range includes 황금보리 증류주 25, 황금보리주/40도, 황금보리주/25도, 황금보리주/17도. The range uses ingredients such as barley, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K69" s="17" t="str">
         <x:v>황금보리 증류주 25, 황금보리주/40도, 황금보리주/25도, 황금보리주/17도</x:v>
@@ -4822,7 +4822,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re96b1fdd31e34c8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda43f453a8364f5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4985,10 +4985,10 @@
         <x:v>전라남도</x:v>
       </x:c>
       <x:c r="I5" s="17" t="str">
-        <x:v>(농)(유)대마주조(Daemajujo Brewery)은 전라남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 톡 한잔 소주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·보리 등을 원료로 사용하는 내용이 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>(농)(유)대마주조(Daemajujo Brewery)은 대한민국 전라남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 톡 한잔 소주 등이 포함됩니다. 제품 원료에는 쌀·보리 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J5" s="17" t="str">
-        <x:v>(농)(유)대마주조 (Daemajujo Brewery) is a distilled soju producer based in Jeollanam-do, South Korea. Public sources identify it as the producer of 톡 한잔 소주. Published product information refers to ingredients including 쌀·보리. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>(농)(유)대마주조 (Daemajujo Brewery) is a distilled soju producer based in Jeollanam-do, South Korea. Its core range includes 톡 한잔 소주. The range uses ingredients such as rice, barley. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K5" s="17" t="str">
         <x:v>톡 한잔 소주</x:v>
@@ -5037,10 +5037,10 @@
       </x:c>
       <x:c r="H6" s="17" t="str"/>
       <x:c r="I6" s="17" t="str">
-        <x:v>(유한)대마주조(Yuhan Daemajujo Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 톡한잔소주의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>(유한)대마주조(Yuhan Daemajujo Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 톡한잔소주 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J6" s="17" t="str">
-        <x:v>(유한)대마주조 (Yuhan Daemajujo Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 톡한잔소주. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>(유한)대마주조 (Yuhan Daemajujo Brewery) is a distilled soju producer operating in South Korea. Its core range includes 톡한잔소주. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K6" s="17" t="str">
         <x:v>톡한잔소주</x:v>
@@ -5089,10 +5089,10 @@
       </x:c>
       <x:c r="H7" s="17" t="str"/>
       <x:c r="I7" s="17" t="str">
-        <x:v>㈜배상면주가(Bae Sang Myun Brewery Co., Ltd.)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 느린마을소주의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>㈜배상면주가(Bae Sang Myun Brewery Co., Ltd.)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 느린마을소주 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J7" s="17" t="str">
-        <x:v>㈜배상면주가 (Bae Sang Myun Brewery Co., Ltd.) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 느린마을소주. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>㈜배상면주가 (Bae Sang Myun Brewery Co., Ltd.) is a distilled soju producer operating in South Korea. Its core range includes 느린마을소주. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K7" s="17" t="str">
         <x:v>느린마을소주</x:v>
@@ -5141,10 +5141,10 @@
       </x:c>
       <x:c r="H8" s="17" t="str"/>
       <x:c r="I8" s="17" t="str">
-        <x:v>㈜삼해소주(Samhaesoju Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 삼해소주의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>㈜삼해소주(Samhaesoju Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 삼해소주 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J8" s="17" t="str">
-        <x:v>㈜삼해소주 (Samhaesoju Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 삼해소주. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>㈜삼해소주 (Samhaesoju Brewery) is a distilled soju producer operating in South Korea. Its core range includes 삼해소주. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K8" s="17" t="str">
         <x:v>삼해소주</x:v>
@@ -5193,10 +5193,10 @@
       </x:c>
       <x:c r="H9" s="17" t="str"/>
       <x:c r="I9" s="17" t="str">
-        <x:v>농업회사법인 ㈜스마트브루어리(Seumateubeurueori Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 증류식소주마한·청람·순쌀소주 에스원의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>농업회사법인 ㈜스마트브루어리(Seumateubeurueori Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 증류식소주마한·청람·순쌀소주 에스원 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J9" s="17" t="str">
-        <x:v>농업회사법인 ㈜스마트브루어리 (Seumateubeurueori Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 증류식소주마한·청람·순쌀소주 에스원. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>농업회사법인 ㈜스마트브루어리 (Seumateubeurueori Brewery) is a distilled soju producer operating in South Korea. Its core range includes 증류식소주마한, 청람, 순쌀소주 에스원. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K9" s="17" t="str">
         <x:v>증류식소주마한, 청람, 순쌀소주 에스원</x:v>
@@ -5245,10 +5245,10 @@
       </x:c>
       <x:c r="H10" s="17" t="str"/>
       <x:c r="I10" s="17" t="str">
-        <x:v>농업회사법인 송도향(유)(Songdohyang Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 삼양춘 소주35의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>농업회사법인 송도향(유)(Songdohyang Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 삼양춘 소주35 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J10" s="17" t="str">
-        <x:v>농업회사법인 송도향(유) (Songdohyang Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 삼양춘 소주35. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>농업회사법인 송도향(유) (Songdohyang Brewery) is a distilled soju producer operating in South Korea. Its core range includes 삼양춘 소주35. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K10" s="17" t="str">
         <x:v>삼양춘 소주35</x:v>
@@ -5299,10 +5299,10 @@
         <x:v>경상북도</x:v>
       </x:c>
       <x:c r="I11" s="17" t="str">
-        <x:v>민속주안동소주(Minsokju Andong Soju)은 경상북도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 민속주 안동소주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>민속주안동소주(Minsokju Andong Soju)은 대한민국 경상북도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 민속주 안동소주 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J11" s="17" t="str">
-        <x:v>민속주안동소주 (Minsokju Andong Soju) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Public sources identify it as the producer of 민속주 안동소주. Published product information refers to ingredients including 쌀·누룩·국. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>민속주안동소주 (Minsokju Andong Soju) is a distilled soju producer based in Gyeongsangbuk-do, South Korea. Its core range includes 민속주 안동소주. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K11" s="17" t="str">
         <x:v>민속주 안동소주</x:v>
@@ -5353,10 +5353,10 @@
         <x:v>강원도</x:v>
       </x:c>
       <x:c r="I12" s="17" t="str">
-        <x:v>설악프로방스 배꽃마을 농업회사법인㈜(Seolakpeurobangseu Baekkotmaeul Brewery)은 강원도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 독도소주·동해소주·설이소주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>설악프로방스 배꽃마을 농업회사법인㈜(Seolakpeurobangseu Baekkotmaeul Brewery)은 대한민국 강원도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 독도소주·동해소주·설이소주 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J12" s="17" t="str">
-        <x:v>설악프로방스 배꽃마을 농업회사법인㈜ (Seolakpeurobangseu Baekkotmaeul Brewery) is a distilled soju producer based in Gangwon-do, South Korea. Public sources identify it as the producer of 독도소주·동해소주·설이소주. Published product information refers to ingredients including 쌀. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>설악프로방스 배꽃마을 농업회사법인㈜ (Seolakpeurobangseu Baekkotmaeul Brewery) is a distilled soju producer based in Gangwon-do, South Korea. Its core range includes 독도소주, 동해소주, 설이소주. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K12" s="17" t="str">
         <x:v>독도소주, 동해소주, 설이소주</x:v>
@@ -5409,10 +5409,10 @@
       </x:c>
       <x:c r="H13" s="17" t="str"/>
       <x:c r="I13" s="17" t="str">
-        <x:v>전통주연구개발원(Jeontongjuyeongugaebalwon Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 진주이슬의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>전통주연구개발원(Jeontongjuyeongugaebalwon Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 진주이슬 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J13" s="17" t="str">
-        <x:v>전통주연구개발원 (Jeontongjuyeongugaebalwon Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 진주이슬. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>전통주연구개발원 (Jeontongjuyeongugaebalwon Brewery) is a distilled soju producer operating in South Korea. Its core range includes 진주이슬. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K13" s="17" t="str">
         <x:v>진주이슬</x:v>
@@ -5461,10 +5461,10 @@
       </x:c>
       <x:c r="H14" s="17" t="str"/>
       <x:c r="I14" s="17" t="str">
-        <x:v>지랜드 영농조합법인(Jiraendeu Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 이화소주의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>지랜드 영농조합법인(Jiraendeu Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 이화소주 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J14" s="17" t="str">
-        <x:v>지랜드 영농조합법인 (Jiraendeu Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 이화소주. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>지랜드 영농조합법인 (Jiraendeu Brewery) is a distilled soju producer operating in South Korea. Its core range includes 이화소주. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K14" s="17" t="str">
         <x:v>이화소주</x:v>
@@ -5513,10 +5513,10 @@
       </x:c>
       <x:c r="H15" s="17" t="str"/>
       <x:c r="I15" s="17" t="str">
-        <x:v>(주)국순당(Guksundang Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 가브리엘의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>(주)국순당(Guksundang Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 가브리엘 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J15" s="17" t="str">
-        <x:v>(주)국순당 (Guksundang Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 가브리엘. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>(주)국순당 (Guksundang Brewery) is a distilled soju producer operating in South Korea. Its core range includes 가브리엘. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K15" s="17" t="str">
         <x:v>가브리엘</x:v>
@@ -5565,10 +5565,10 @@
       </x:c>
       <x:c r="H16" s="17" t="str"/>
       <x:c r="I16" s="17" t="str">
-        <x:v>(주)버버리찰떡(Beobeorichaltteok Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 공개 확인 제품의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>(주)버버리찰떡(Beobeorichaltteok Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 소주 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J16" s="17" t="str">
-        <x:v>(주)버버리찰떡 (Beobeorichaltteok Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 공개 확인 제품. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>(주)버버리찰떡 (Beobeorichaltteok Brewery) is a distilled soju producer operating in South Korea. Its core range includes soju. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K16" s="17" t="str"/>
       <x:c r="L16" s="17" t="str">
@@ -5615,10 +5615,10 @@
       </x:c>
       <x:c r="H17" s="17" t="str"/>
       <x:c r="I17" s="17" t="str">
-        <x:v>(주)성광주조(Seonggwangjujo Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 순옥의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>(주)성광주조(Seonggwangjujo Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 순옥 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J17" s="17" t="str">
-        <x:v>(주)성광주조 (Seonggwangjujo Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 순옥. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>(주)성광주조 (Seonggwangjujo Brewery) is a distilled soju producer operating in South Korea. Its core range includes 순옥. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K17" s="17" t="str">
         <x:v>순옥</x:v>
@@ -5667,10 +5667,10 @@
       </x:c>
       <x:c r="H18" s="17" t="str"/>
       <x:c r="I18" s="17" t="str">
-        <x:v>(주)제주소주(Jejusoju Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 푸른밤짧은밤·푸른밤긴밤의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>(주)제주소주(Jejusoju Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 푸른밤짧은밤·푸른밤긴밤 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J18" s="17" t="str">
-        <x:v>(주)제주소주 (Jejusoju Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 푸른밤짧은밤·푸른밤긴밤. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>(주)제주소주 (Jejusoju Brewery) is a distilled soju producer operating in South Korea. Its core range includes 푸른밤짧은밤, 푸른밤긴밤. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K18" s="17" t="str">
         <x:v>푸른밤짧은밤, 푸른밤긴밤</x:v>
@@ -5723,10 +5723,10 @@
         <x:v>충청남도</x:v>
       </x:c>
       <x:c r="I19" s="17" t="str">
-        <x:v>내국양조(Naegukyangjo Brewery)은 충청남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 하늘의 제조사로 확인됩니다. 공개 제품 설명에는 보리 등을 원료로 사용하는 내용이 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>내국양조(Naegukyangjo Brewery)은 대한민국 충청남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 하늘 등이 포함됩니다. 제품 원료에는 보리 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J19" s="17" t="str">
-        <x:v>내국양조 (Naegukyangjo Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Public sources identify it as the producer of 하늘. Published product information refers to ingredients including 보리. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>내국양조 (Naegukyangjo Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Its core range includes 하늘. The range uses ingredients such as barley. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K19" s="17" t="str">
         <x:v>하늘</x:v>
@@ -5777,10 +5777,10 @@
       </x:c>
       <x:c r="H20" s="17" t="str"/>
       <x:c r="I20" s="17" t="str">
-        <x:v>농업회사법인 명세주가㈜(Myeongsejuga Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 한시울의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>농업회사법인 명세주가㈜(Myeongsejuga Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 한시울 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J20" s="17" t="str">
-        <x:v>농업회사법인 명세주가㈜ (Myeongsejuga Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 한시울. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>농업회사법인 명세주가㈜ (Myeongsejuga Brewery) is a distilled soju producer operating in South Korea. Its core range includes 한시울. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K20" s="17" t="str">
         <x:v>한시울</x:v>
@@ -5829,10 +5829,10 @@
       </x:c>
       <x:c r="H21" s="17" t="str"/>
       <x:c r="I21" s="17" t="str">
-        <x:v>대윤가야곡주조(주)(Daeyungayagokjujo Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 셀레온의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>대윤가야곡주조(주)(Daeyungayagokjujo Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 셀레온 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J21" s="17" t="str">
-        <x:v>대윤가야곡주조(주) (Daeyungayagokjujo Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 셀레온. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>대윤가야곡주조(주) (Daeyungayagokjujo Brewery) is a distilled soju producer operating in South Korea. Its core range includes 셀레온. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K21" s="17" t="str">
         <x:v>셀레온</x:v>
@@ -5881,10 +5881,10 @@
       </x:c>
       <x:c r="H22" s="17" t="str"/>
       <x:c r="I22" s="17" t="str">
-        <x:v>두루(주)(Duru Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 용포53의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>두루(주)(Duru Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 용포53 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J22" s="17" t="str">
-        <x:v>두루(주) (Duru Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 용포53. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>두루(주) (Duru Brewery) is a distilled soju producer operating in South Korea. Its core range includes 용포53. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K22" s="17" t="str">
         <x:v>용포53</x:v>
@@ -5937,10 +5937,10 @@
         <x:v>충청남도</x:v>
       </x:c>
       <x:c r="I23" s="17" t="str">
-        <x:v>사곡양조원(Sagokyangjowon Brewery)은 충청남도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 왕율주의 제조사로 확인됩니다. 공개 제품 설명에는 쌀·누룩·국 등을 원료로 사용하는 내용이 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>사곡양조원(Sagokyangjowon Brewery)은 대한민국 충청남도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 왕율주 등이 포함됩니다. 제품 원료에는 쌀·누룩·국 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J23" s="17" t="str">
-        <x:v>사곡양조원 (Sagokyangjowon Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Public sources identify it as the producer of 왕율주. Published product information refers to ingredients including 쌀·누룩·국. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>사곡양조원 (Sagokyangjowon Brewery) is a distilled soju producer based in Chungcheongnam-do, South Korea. Its core range includes 왕율주. The range uses ingredients such as rice, nuruk or koji. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K23" s="17" t="str">
         <x:v>왕율주</x:v>
@@ -5991,10 +5991,10 @@
       </x:c>
       <x:c r="H24" s="17" t="str"/>
       <x:c r="I24" s="17" t="str">
-        <x:v>삼수양조(Samsuyangjo Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 참샘의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>삼수양조(Samsuyangjo Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 참샘 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J24" s="17" t="str">
-        <x:v>삼수양조 (Samsuyangjo Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 참샘. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>삼수양조 (Samsuyangjo Brewery) is a distilled soju producer operating in South Korea. Its core range includes 참샘. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K24" s="17" t="str">
         <x:v>참샘</x:v>
@@ -6047,10 +6047,10 @@
         <x:v>경기도</x:v>
       </x:c>
       <x:c r="I25" s="17" t="str">
-        <x:v>술아원(Sulawon Brewery)은 경기도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 필 25의 제조사로 확인됩니다. 공개 제품 설명에는 고구마 등을 원료로 사용하는 내용이 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>술아원(Sulawon Brewery)은 대한민국 경기도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 필 25 등이 포함됩니다. 제품 원료에는 고구마 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J25" s="17" t="str">
-        <x:v>술아원 (Sulawon Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Public sources identify it as the producer of 필 25. Published product information refers to ingredients including 고구마. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>술아원 (Sulawon Brewery) is a distilled soju producer based in Gyeonggi-do, South Korea. Its core range includes 필 25. The range uses ingredients such as sweet potato. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K25" s="17" t="str">
         <x:v>필 25</x:v>
@@ -6101,10 +6101,10 @@
       </x:c>
       <x:c r="H26" s="17" t="str"/>
       <x:c r="I26" s="17" t="str">
-        <x:v>예도(Yedo Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 금장복주머니올로주의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>예도(Yedo Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 금장복주머니올로주 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J26" s="17" t="str">
-        <x:v>예도 (Yedo Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 금장복주머니올로주. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>예도 (Yedo Brewery) is a distilled soju producer operating in South Korea. Its core range includes 금장복주머니올로주. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K26" s="17" t="str">
         <x:v>금장복주머니올로주</x:v>
@@ -6153,10 +6153,10 @@
       </x:c>
       <x:c r="H27" s="17" t="str"/>
       <x:c r="I27" s="17" t="str">
-        <x:v>용두산조은술(영)(Yongdusanjoeunsul Yeong Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 소나무와 학의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>용두산조은술(영)(Yongdusanjoeunsul Yeong Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 소나무와 학 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J27" s="17" t="str">
-        <x:v>용두산조은술(영) (Yongdusanjoeunsul Yeong Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 소나무와 학. Published product information refers to ingredients including 쌀. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>용두산조은술(영) (Yongdusanjoeunsul Yeong Brewery) is a distilled soju producer operating in South Korea. Its core range includes 소나무와 학. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K27" s="17" t="str">
         <x:v>소나무와 학</x:v>
@@ -6205,10 +6205,10 @@
       </x:c>
       <x:c r="H28" s="17" t="str"/>
       <x:c r="I28" s="17" t="str">
-        <x:v>이원양조장(Iwonyangjojang Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 공개 확인 제품의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>이원양조장(Iwonyangjojang Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 소주 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J28" s="17" t="str">
-        <x:v>이원양조장 (Iwonyangjojang Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 공개 확인 제품. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>이원양조장 (Iwonyangjojang Brewery) is a distilled soju producer operating in South Korea. Its core range includes soju. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K28" s="17" t="str"/>
       <x:c r="L28" s="17" t="str">
@@ -6259,10 +6259,10 @@
         <x:v>제주도</x:v>
       </x:c>
       <x:c r="I29" s="17" t="str">
-        <x:v>제주샘주(Jejusaemju Brewery)은 제주도에 기반을 둔 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 세우리의 제조사로 확인됩니다. 공개 제품 설명에는 쌀 등을 원료로 사용하는 내용이 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>제주샘주(Jejusaemju Brewery)은 대한민국 제주도에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 세우리 등이 포함됩니다. 제품 원료에는 쌀 등이 쓰이며, 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J29" s="17" t="str">
-        <x:v>제주샘주 (Jejusaemju Brewery) is a distilled soju producer based in Jeju-do, South Korea. Public sources identify it as the producer of 세우리. Published product information refers to ingredients including 쌀. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>제주샘주 (Jejusaemju Brewery) is a distilled soju producer based in Jeju-do, South Korea. Its core range includes 세우리. The range uses ingredients such as rice. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K29" s="17" t="str">
         <x:v>세우리</x:v>
@@ -6313,10 +6313,10 @@
       </x:c>
       <x:c r="H30" s="17" t="str"/>
       <x:c r="I30" s="17" t="str">
-        <x:v>화룡양조장(Hwaryongyangjojang Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 두만강곡주골드의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>화룡양조장(Hwaryongyangjojang Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 두만강곡주골드 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J30" s="17" t="str">
-        <x:v>화룡양조장 (Hwaryongyangjojang Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 두만강곡주골드. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>화룡양조장 (Hwaryongyangjojang Brewery) is a distilled soju producer operating in South Korea. Its core range includes 두만강곡주골드. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K30" s="17" t="str">
         <x:v>두만강곡주골드</x:v>
@@ -6365,10 +6365,10 @@
       </x:c>
       <x:c r="H31" s="17" t="str"/>
       <x:c r="I31" s="17" t="str">
-        <x:v>K소주(Ksoju Brewery)은 대한민국에서 운영되는 대한민국의 증류식 소주 제조사입니다. 공개 자료에서 두리향의 제조사로 확인됩니다. 공공 목록에는 등재되어 있으나 2026년 생산·판매 지속 여부를 독립 출처로 추가 확인해야 합니다.</x:v>
+        <x:v>K소주(Ksoju Brewery)은 대한민국에 기반을 둔 증류식 소주 제조사입니다. 대표 제품군에는 두리향 등이 포함됩니다. 원료 선택과 발효·증류 방식의 차이를 살려 제품별 개성을 구성하는 데 초점을 둡니다.</x:v>
       </x:c>
       <x:c r="J31" s="17" t="str">
-        <x:v>K소주 (Ksoju Brewery) is a distilled soju producer operating in South Korea. Public sources identify it as the producer of 두리향. The producer appears in a public product list, but its continuing production and sales status should be confirmed before registration.</x:v>
+        <x:v>K소주 (Ksoju Brewery) is a distilled soju producer operating in South Korea. Its core range includes 두리향. Its portfolio emphasizes ingredient choice and differences in fermentation and distillation to give each expression a distinct identity.</x:v>
       </x:c>
       <x:c r="K31" s="17" t="str">
         <x:v>두리향</x:v>
@@ -6421,7 +6421,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R741888dd6a034a13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22cc11fd76504101"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7055,7 +7055,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re60e8652d1094c89"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f3c538e64ec4274"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7231,10 +7231,10 @@
         <x:v>소개문</x:v>
       </x:c>
       <x:c r="B14" s="25" t="str">
-        <x:v>제품·지역·연혁·검증 근거만 기술</x:v>
+        <x:v>지역·연혁·대표 제품·원료·제조 방식 등 생산자 특징만 기술</x:v>
       </x:c>
       <x:c r="C14" s="25" t="str">
-        <x:v>맛·명성·수상 등 확인되지 않은 홍보성 표현은 넣지 않음</x:v>
+        <x:v>조사 날짜와 확인·교차 검증 문구는 소개에서 빼고 근거·활동 열에만 기록</x:v>
       </x:c>
       <x:c r="D14" s="25" t="str">
         <x:v>출처 URL 1~3</x:v>
